--- a/SGI_Sistema-de-gestao-integrado/SGA_Sistema-de-gestao-ambiental/Registos_SGA_Plasticom/SGA-04_Requisitos_Legais_Conformidade.xlsx
+++ b/SGI_Sistema-de-gestao-integrado/SGA_Sistema-de-gestao-ambiental/Registos_SGA_Plasticom/SGA-04_Requisitos_Legais_Conformidade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project Portfolios\manufacturing-performance-analytics\SGI_Sistema-de-gestao-integrado\SGA_Sistema-de-gestao-ambiental\Registos_SGA_Plasticom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{271DDB38-24FC-4564-8133-E1E3ED65E330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBF241FC-7369-4B51-B9DE-F0121ABC77C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1325,7 +1325,7 @@
     <t>Instalações com consumo ≥ 500 tep/ano: registo, auditoria energética periódica e Plano de Racionalização do Consumo de Energia (PREn) com metas de intensidade energética e relatórios de execução.</t>
   </si>
   <si>
-    <t>Consumo ≈ 7,2 GWh/ano ≈ 1.540 tep/ano (fator 0,215 tep/MWh).</t>
+    <t>Consumo ≈ 7,8 GWh em 2026 ≈ 1.680 tep/ano (fator 0,215 tep/MWh).</t>
   </si>
   <si>
     <t>INJ; SOP; UTL; GER</t>
